--- a/outputs/05_benchmark_signals/tables_v_viii/us/table_viii_image_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/us/table_viii_image_logit.xlsx
@@ -490,35 +490,35 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.00*** (6.9)</t>
+          <t>2.24*** (7.2)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.00*** (5.1)</t>
+          <t>0.99*** (6.8)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.00*** (10.6)</t>
+          <t>2.61*** (11.2)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.00*** (5.8)</t>
+          <t>1.15*** (6.8)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.00*** (4.2)</t>
+          <t>1.06*** (4.0)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.00*** (4.2)</t>
+          <t>0.70*** (4.4)</t>
         </is>
       </c>
     </row>
@@ -530,50 +530,50 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.00*** (-19.0)</t>
+          <t>-2.03*** (-18.5)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.00*** (-17.5)</t>
+          <t>-0.85*** (-21.9)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.00*** (4.0)</t>
+          <t>0.05** (2.2)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.00 (-1.5)</t>
+          <t>-0.14*** (-3.4)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.00 (-1.1)</t>
+          <t>-0.12*** (-2.7)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>-0.06 (-1.2)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>-0.05 (-1.0)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.02 (0.4)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.00 (0.7)</t>
+          <t>0.02 (0.4)</t>
         </is>
       </c>
     </row>
@@ -585,50 +585,50 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.00 (1.4)</t>
+          <t>0.19 (1.5)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.00*** (40.4)</t>
+          <t>1.68*** (50.4)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.00*** (12.7)</t>
+          <t>0.29*** (9.8)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.00* (1.8)</t>
+          <t>0.08** (2.0)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.00* (1.7)</t>
+          <t>0.07* (1.8)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.00** (2.1)</t>
+          <t>0.09** (2.3)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.00* (1.7)</t>
+          <t>0.07* (1.8)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.00 (0.9)</t>
+          <t>0.03 (0.9)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.03 (0.8)</t>
         </is>
       </c>
     </row>
@@ -640,50 +640,50 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.00*** (3.8)</t>
+          <t>0.20** (2.0)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.00*** (-25.1)</t>
+          <t>-0.91*** (-29.1)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00*** (3.1)</t>
+          <t>0.01 (0.6)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>-0.01 (-0.3)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>-0.01 (-0.3)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.00 (1.6)</t>
+          <t>0.06* (1.8)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.00* (1.8)</t>
+          <t>0.07** (2.2)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.00*** (3.6)</t>
+          <t>0.12*** (3.5)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.00*** (3.5)</t>
+          <t>0.12*** (3.5)</t>
         </is>
       </c>
     </row>
@@ -695,50 +695,50 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.00 (-0.9)</t>
+          <t>-0.14 (-1.3)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.00*** (5.9)</t>
+          <t>-0.60*** (-20.7)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.00* (-1.8)</t>
+          <t>-0.11*** (-4.4)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.00*** (3.2)</t>
+          <t>0.05 (1.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.00*** (3.0)</t>
+          <t>0.05 (1.4)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>-0.01 (-0.2)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>0.00 (0.0)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.00 (0.5)</t>
+          <t>-0.01 (-0.3)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.00 (0.5)</t>
+          <t>-0.01 (-0.3)</t>
         </is>
       </c>
     </row>
@@ -750,50 +750,50 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.00*** (5.6)</t>
+          <t>-0.42*** (-4.2)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.00*** (-28.6)</t>
+          <t>-1.66*** (-59.3)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.5)</t>
+          <t>-0.15*** (-7.3)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>0.06* (1.9)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>0.06** (2.1)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.00 (0.1)</t>
+          <t>0.04 (1.2)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.06* (1.8)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.00 (0.7)</t>
+          <t>0.01 (0.1)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.01 (0.2)</t>
         </is>
       </c>
     </row>
@@ -805,50 +805,50 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.00*** (20.8)</t>
+          <t>6.46*** (20.3)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.00*** (64.5)</t>
+          <t>7.09*** (89.8)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.00*** (19.4)</t>
+          <t>1.09*** (20.8)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.00*** (12.9)</t>
+          <t>0.59*** (14.3)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.00*** (10.8)</t>
+          <t>0.50*** (11.5)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.00*** (8.0)</t>
+          <t>0.34*** (8.9)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.00*** (5.8)</t>
+          <t>0.25*** (6.1)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.00*** (5.4)</t>
+          <t>0.19*** (6.1)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.00*** (4.9)</t>
+          <t>0.17*** (5.6)</t>
         </is>
       </c>
     </row>
@@ -860,50 +860,50 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.00*** (6.3)</t>
+          <t>1.17*** (4.0)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.00*** (70.7)</t>
+          <t>2.26*** (77.1)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.00*** (16.6)</t>
+          <t>0.71*** (17.8)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.00* (1.7)</t>
+          <t>0.02 (0.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.00 (1.6)</t>
+          <t>0.02 (0.6)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.00 (0.1)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>-0.03 (-0.7)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.00 (1.0)</t>
+          <t>0.03 (0.8)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.02 (0.5)</t>
         </is>
       </c>
     </row>
@@ -915,28 +915,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.00*** (4.4)</t>
+          <t>0.92*** (3.6)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.00*** (-9.3)</t>
+          <t>-1.11*** (-27.3)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.00*** (12.2)</t>
+          <t>0.33*** (11.1)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.00 (0.7)</t>
+          <t>0.02 (0.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.00 (0.3)</t>
+          <t>0.00 (0.0)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -947,18 +947,18 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.00 (0.0)</t>
+          <t>0.01 (0.2)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.00* (-1.7)</t>
+          <t>-0.05 (-1.2)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-0.00* (-1.9)</t>
+          <t>-0.05 (-1.4)</t>
         </is>
       </c>
     </row>
@@ -970,50 +970,50 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.00*** (5.2)</t>
+          <t>1.35*** (5.0)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.00*** (2.8)</t>
+          <t>0.77*** (16.6)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.00*** (-2.8)</t>
+          <t>-0.10*** (-3.5)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.00* (1.9)</t>
+          <t>0.04 (1.3)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.00 (1.6)</t>
+          <t>0.03 (1.0)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.00 (1.0)</t>
+          <t>0.03 (0.7)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.00 (0.8)</t>
+          <t>0.02 (0.5)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.00 (0.1)</t>
+          <t>0.01 (0.1)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.00 (0.1)</t>
+          <t>0.01 (0.2)</t>
         </is>
       </c>
     </row>
@@ -1025,50 +1025,50 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.00** (2.4)</t>
+          <t>0.71*** (3.0)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.00*** (13.4)</t>
+          <t>1.21*** (29.6)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.00*** (-6.2)</t>
+          <t>-0.10*** (-3.4)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.00* (1.7)</t>
+          <t>0.03 (0.9)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.00* (1.7)</t>
+          <t>0.03 (1.0)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.00 (0.1)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.00 (0.2)</t>
+          <t>-0.01 (-0.3)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.00 (-0.5)</t>
+          <t>0.02 (0.5)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-0.00 (-0.4)</t>
+          <t>0.02 (0.5)</t>
         </is>
       </c>
     </row>
@@ -1080,50 +1080,50 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.00*** (19.5)</t>
+          <t>5.49*** (18.0)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.00*** (46.7)</t>
+          <t>3.62*** (72.7)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.0)</t>
+          <t>0.02 (0.4)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.00*** (15.4)</t>
+          <t>0.75*** (17.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.00*** (14.6)</t>
+          <t>0.68*** (15.1)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.00*** (10.4)</t>
+          <t>0.49*** (12.7)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.00*** (9.4)</t>
+          <t>0.44*** (11.0)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.00*** (5.4)</t>
+          <t>0.33*** (6.6)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.00*** (5.4)</t>
+          <t>0.33*** (6.6)</t>
         </is>
       </c>
     </row>
@@ -1135,50 +1135,50 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.00*** (4.7)</t>
+          <t>0.91*** (3.1)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.00*** (59.7)</t>
+          <t>2.62*** (74.7)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.00*** (17.3)</t>
+          <t>1.05*** (17.7)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.00*** (4.7)</t>
+          <t>0.12*** (3.1)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.00*** (4.8)</t>
+          <t>0.12*** (3.2)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.00*** (3.5)</t>
+          <t>0.09** (2.6)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.00*** (2.6)</t>
+          <t>0.06 (1.6)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.00*** (3.0)</t>
+          <t>0.11*** (2.8)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.00*** (2.6)</t>
+          <t>0.09** (2.3)</t>
         </is>
       </c>
     </row>
@@ -1190,50 +1190,50 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.00** (2.5)</t>
+          <t>0.43 (1.6)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.00 (-1.5)</t>
+          <t>0.16*** (3.4)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.00*** (-7.3)</t>
+          <t>-0.19*** (-5.3)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.00*** (2.7)</t>
+          <t>0.07* (1.7)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.00** (2.5)</t>
+          <t>0.07 (1.5)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>0.00 (0.1)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>0.00 (0.1)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.00 (0.5)</t>
+          <t>0.00 (0.1)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.00 (0.5)</t>
+          <t>0.01 (0.1)</t>
         </is>
       </c>
     </row>
@@ -1245,50 +1245,50 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.00*** (6.1)</t>
+          <t>1.99*** (6.7)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.00*** (8.0)</t>
+          <t>0.68*** (17.0)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.00*** (-7.2)</t>
+          <t>-0.21*** (-5.9)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.03 (0.8)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.00 (0.9)</t>
+          <t>0.01 (0.4)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.00** (2.3)</t>
+          <t>0.10** (2.6)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.00** (2.3)</t>
+          <t>0.09** (2.4)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.00 (1.1)</t>
+          <t>0.09** (2.1)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>0.09** (2.1)</t>
         </is>
       </c>
     </row>
@@ -1300,50 +1300,50 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>0.74*** (2.8)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.00*** (-20.2)</t>
+          <t>-1.11*** (-30.4)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.9)</t>
+          <t>-0.32*** (-8.7)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.00 (1.0)</t>
+          <t>-0.02 (-0.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.00 (1.2)</t>
+          <t>-0.01 (-0.2)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.00* (1.8)</t>
+          <t>0.02 (0.7)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.00** (2.0)</t>
+          <t>0.04 (1.1)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.00*** (3.1)</t>
+          <t>0.10*** (2.6)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.00*** (3.2)</t>
+          <t>0.11*** (2.8)</t>
         </is>
       </c>
     </row>
@@ -1355,50 +1355,50 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-0.00*** (-17.5)</t>
+          <t>-8.45*** (-10.7)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.00*** (-69.2)</t>
+          <t>-13.68*** (-150.4)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.00*** (-21.0)</t>
+          <t>-2.13*** (-21.5)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.00*** (-18.0)</t>
+          <t>-1.42*** (-17.2)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.00*** (-16.9)</t>
+          <t>-1.27*** (-15.4)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.00*** (-12.5)</t>
+          <t>-0.76*** (-9.4)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.00*** (-9.7)</t>
+          <t>-0.60*** (-7.2)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.00*** (-4.8)</t>
+          <t>-0.28*** (-3.4)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-0.00*** (-4.3)</t>
+          <t>-0.25*** (-3.0)</t>
         </is>
       </c>
     </row>
@@ -1410,50 +1410,50 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>-0.00*** (-4.5)</t>
+          <t>-0.37 (-0.6)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.00*** (-9.7)</t>
+          <t>-0.78*** (-13.8)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>-0.00 (-0.0)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.00 (-0.4)</t>
+          <t>-0.09 (-1.2)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>-0.09 (-1.2)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.00* (-2.0)</t>
+          <t>-0.18*** (-2.8)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.00* (-1.9)</t>
+          <t>-0.18*** (-2.7)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.00** (-2.1)</t>
+          <t>-0.12 (-1.5)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-0.00** (-2.1)</t>
+          <t>-0.12 (-1.5)</t>
         </is>
       </c>
     </row>
@@ -1465,50 +1465,50 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-0.00*** (-2.6)</t>
+          <t>0.14 (0.2)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.00*** (17.1)</t>
+          <t>0.15*** (2.7)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.00*** (3.9)</t>
+          <t>0.07 (1.3)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.00 (-1.5)</t>
+          <t>-0.18* (-1.9)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.00 (-1.2)</t>
+          <t>-0.15 (-1.6)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.00 (-0.5)</t>
+          <t>-0.06 (-0.8)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.00 (-0.6)</t>
+          <t>-0.06 (-0.8)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.00 (-0.5)</t>
+          <t>-0.03 (-0.4)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-0.00 (-0.6)</t>
+          <t>-0.03 (-0.5)</t>
         </is>
       </c>
     </row>
@@ -1520,50 +1520,50 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.4)</t>
+          <t>-0.47 (-0.6)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.00*** (-6.3)</t>
+          <t>-1.03*** (-26.6)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.00*** (3.4)</t>
+          <t>0.02 (0.4)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.00 (-0.4)</t>
+          <t>-0.14* (-1.9)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>-0.13* (-1.9)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.00 (-0.6)</t>
+          <t>-0.14** (-2.2)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.00 (-0.6)</t>
+          <t>-0.13** (-2.0)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.00 (-1.5)</t>
+          <t>-0.11 (-1.5)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-0.00 (-1.5)</t>
+          <t>-0.11 (-1.6)</t>
         </is>
       </c>
     </row>
@@ -1575,50 +1575,50 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>-0.00*** (-17.4)</t>
+          <t>-15.44*** (-7.7)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.00*** (-14.2)</t>
+          <t>-0.59*** (-3.1)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-0.00*** (-14.1)</t>
+          <t>-1.75*** (-9.4)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.00 (-0.7)</t>
+          <t>0.87*** (3.1)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.00 (-0.1)</t>
+          <t>0.95*** (3.4)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.00 (-0.5)</t>
+          <t>0.54* (1.7)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>0.55* (1.7)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.00 (0.2)</t>
+          <t>-0.02 (-0.1)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>0.01 (0.0)</t>
         </is>
       </c>
     </row>
@@ -1630,50 +1630,50 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.00*** (3.1)</t>
+          <t>1.15*** (2.7)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.00*** (31.5)</t>
+          <t>4.10*** (25.8)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.00*** (8.8)</t>
+          <t>1.32*** (7.8)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.00** (-2.0)</t>
+          <t>-0.76** (-2.4)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.00** (-2.1)</t>
+          <t>-0.79** (-2.5)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.00 (-0.6)</t>
+          <t>-0.22 (-0.7)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-0.00 (-0.9)</t>
+          <t>-0.27 (-0.8)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>-0.04 (-0.1)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-0.00 (-0.4)</t>
+          <t>-0.06 (-0.2)</t>
         </is>
       </c>
     </row>
@@ -1685,50 +1685,50 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>-0.00*** (-4.5)</t>
+          <t>0.94*** (3.5)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.00*** (-21.4)</t>
+          <t>0.40*** (3.3)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.00** (2.4)</t>
+          <t>0.70*** (4.7)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.00 (0.5)</t>
+          <t>0.04 (0.2)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.03 (0.1)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>-0.29 (-1.6)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-0.00 (-0.0)</t>
+          <t>-0.29* (-1.6)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.00 (0.7)</t>
+          <t>0.15 (0.7)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.00 (0.7)</t>
+          <t>0.14 (0.7)</t>
         </is>
       </c>
     </row>
@@ -1740,50 +1740,50 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.00*** (5.1)</t>
+          <t>-0.20 (-1.0)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.00*** (15.9)</t>
+          <t>-0.67*** (-6.9)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.00 (1.0)</t>
+          <t>-0.12 (-0.9)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.25 (1.0)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.00 (0.5)</t>
+          <t>0.25 (1.0)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>0.32 (1.5)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.00 (0.2)</t>
+          <t>0.33 (1.6)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.00 (-0.7)</t>
+          <t>-0.06 (-0.3)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>-0.00 (-0.7)</t>
+          <t>-0.06 (-0.3)</t>
         </is>
       </c>
     </row>
@@ -1795,50 +1795,50 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0.00*** (8.2)</t>
+          <t>1.75*** (11.3)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.00*** (-12.2)</t>
+          <t>-0.13** (-2.5)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-0.00*** (-4.9)</t>
+          <t>-0.27*** (-4.4)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.00 (-0.5)</t>
+          <t>-0.12 (-1.1)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.00 (-0.5)</t>
+          <t>-0.12 (-1.1)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.00 (-0.3)</t>
+          <t>-0.13 (-1.1)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-0.00 (-0.2)</t>
+          <t>-0.13 (-1.1)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00 (-0.7)</t>
+          <t>-0.13 (-1.1)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-0.00 (-0.7)</t>
+          <t>-0.13 (-1.1)</t>
         </is>
       </c>
     </row>
@@ -1850,50 +1850,50 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0.00*** (18.7)</t>
+          <t>1.19*** (19.3)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.00*** (76.4)</t>
+          <t>2.73*** (92.3)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.00*** (6.3)</t>
+          <t>0.19*** (8.2)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.00*** (4.7)</t>
+          <t>0.09*** (5.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.00*** (4.0)</t>
+          <t>0.07*** (4.4)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.00*** (5.9)</t>
+          <t>0.10*** (6.2)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.00*** (4.1)</t>
+          <t>0.07*** (3.9)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.00*** (3.1)</t>
+          <t>0.06*** (3.3)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.00*** (2.9)</t>
+          <t>0.06*** (3.1)</t>
         </is>
       </c>
     </row>
@@ -1905,50 +1905,50 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0.00*** (4.6)</t>
+          <t>0.25*** (4.3)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.00*** (96.7)</t>
+          <t>2.11*** (106.5)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.00*** (23.9)</t>
+          <t>0.80*** (24.5)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.00*** (4.5)</t>
+          <t>0.05*** (4.2)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.00*** (4.5)</t>
+          <t>0.04*** (4.1)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.00** (2.5)</t>
+          <t>0.03** (2.3)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.00 (0.6)</t>
+          <t>0.00 (0.2)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.00*** (2.7)</t>
+          <t>0.03** (2.1)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.00* (2.0)</t>
+          <t>0.02 (1.2)</t>
         </is>
       </c>
     </row>
@@ -1960,50 +1960,50 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0.00*** (5.7)</t>
+          <t>0.20*** (4.2)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.00*** (13.7)</t>
+          <t>0.20*** (13.6)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.00*** (20.2)</t>
+          <t>0.40*** (21.7)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.00*** (2.6)</t>
+          <t>0.02** (2.2)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.00** (2.3)</t>
+          <t>0.02* (1.7)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.00*** (2.6)</t>
+          <t>0.03* (1.9)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.00** (2.5)</t>
+          <t>0.02* (1.7)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.00 (1.4)</t>
+          <t>0.01 (0.8)</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.00 (0.9)</t>
+          <t>0.00 (0.3)</t>
         </is>
       </c>
     </row>
@@ -2015,50 +2015,50 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>-0.00*** (-3.7)</t>
+          <t>-0.20*** (-3.7)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-0.00*** (-14.7)</t>
+          <t>-0.44*** (-21.1)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-0.00*** (-6.1)</t>
+          <t>-0.11*** (-7.8)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.00** (2.1)</t>
+          <t>0.03** (2.1)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.00** (2.2)</t>
+          <t>0.03** (2.3)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.00*** (3.2)</t>
+          <t>0.04*** (2.6)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.00*** (3.4)</t>
+          <t>0.04*** (3.0)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.00** (2.3)</t>
+          <t>0.03** (2.1)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.00** (2.3)</t>
+          <t>0.04** (2.2)</t>
         </is>
       </c>
     </row>
@@ -2070,50 +2070,50 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>-0.00*** (-10.8)</t>
+          <t>-0.42*** (-9.4)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-0.00*** (-17.9)</t>
+          <t>-0.59*** (-22.2)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-0.00 (-1.6)</t>
+          <t>-0.09*** (-6.4)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.00 (0.2)</t>
+          <t>-0.01 (-0.7)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>-0.01 (-0.5)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.00 (0.1)</t>
+          <t>-0.01 (-0.8)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.00 (0.4)</t>
+          <t>-0.00 (-0.2)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.00 (1.3)</t>
+          <t>0.01 (0.4)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.00 (1.3)</t>
+          <t>0.01 (0.5)</t>
         </is>
       </c>
     </row>
@@ -2125,17 +2125,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>36.52</t>
+          <t>45.90</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2313,49 +2313,49 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>5.135789667321288e-05</v>
+        <v>2.238475687979131</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>1.89087795744386e-05</v>
+        <v>0.9880736638442671</v>
       </c>
       <c r="H2" t="n">
-        <v>5.021758292870579e-05</v>
+        <v>2.607513524172602</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>1.833924062740647e-05</v>
+        <v>1.150107005395424</v>
       </c>
       <c r="K2" t="n">
-        <v>2.699501035893195e-05</v>
+        <v>1.057061454389685</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>1.656880524128953e-05</v>
+        <v>0.7048200668419595</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>6.941764717597452</v>
+        <v>7.226908221152295</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>5.125158842099156</v>
+        <v>6.815388040334831</v>
       </c>
       <c r="T2" t="n">
-        <v>10.62179249512781</v>
+        <v>11.22627887111032</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>5.790354066364995</v>
+        <v>6.755959515647544</v>
       </c>
       <c r="W2" t="n">
-        <v>4.179334570814921</v>
+        <v>3.962981606386278</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>4.152662675458465</v>
+        <v>4.392521551811224</v>
       </c>
     </row>
     <row r="3">
@@ -2365,64 +2365,64 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0002223226914490386</v>
+        <v>-2.033210976628718</v>
       </c>
       <c r="C3" t="n">
-        <v>-9.301761107197642e-05</v>
+        <v>-0.8481055814767882</v>
       </c>
       <c r="D3" t="n">
-        <v>1.396663346289551e-05</v>
+        <v>0.05154381531161691</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-8.487583628983853e-06</v>
+        <v>-0.1411282107080065</v>
       </c>
       <c r="G3" t="n">
-        <v>-6.246555042585502e-06</v>
+        <v>-0.1152857032095222</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>-2.161060254387003e-06</v>
+        <v>-0.05573348553041584</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.400061232192107e-06</v>
+        <v>-0.0469768270434592</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>4.866218105321252e-06</v>
+        <v>0.02013955189089983</v>
       </c>
       <c r="M3" t="n">
-        <v>4.812458393090012e-06</v>
+        <v>0.02000592783853306</v>
       </c>
       <c r="N3" t="n">
-        <v>-18.97741508688272</v>
+        <v>-18.54196913954928</v>
       </c>
       <c r="O3" t="n">
-        <v>-17.45859519573368</v>
+        <v>-21.91601222204957</v>
       </c>
       <c r="P3" t="n">
-        <v>3.963636003185387</v>
+        <v>2.229627697009998</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>-1.53251192422477</v>
+        <v>-3.421159469367197</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.115113322185755</v>
+        <v>-2.748130807694765</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>-0.347838208731944</v>
+        <v>-1.22403532262358</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2245105408316813</v>
+        <v>-1.022979558841781</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>0.7500606179426115</v>
+        <v>0.4499921684347623</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7470856773628978</v>
+        <v>0.4486633356482012</v>
       </c>
     </row>
     <row r="4">
@@ -2432,64 +2432,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.826903616777226e-05</v>
+        <v>0.189566371205674</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0002116342785040255</v>
+        <v>1.684568982672148</v>
       </c>
       <c r="D4" t="n">
-        <v>4.832948137775229e-05</v>
+        <v>0.2922750579012481</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>1.025215594491636e-05</v>
+        <v>0.08316217284776221</v>
       </c>
       <c r="G4" t="n">
-        <v>9.448940666509965e-06</v>
+        <v>0.07306151476702917</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>1.022540000709253e-05</v>
+        <v>0.08778702328531564</v>
       </c>
       <c r="J4" t="n">
-        <v>8.116087244600558e-06</v>
+        <v>0.06631395290868715</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>4.598962606904443e-06</v>
+        <v>0.03276444879408861</v>
       </c>
       <c r="M4" t="n">
-        <v>4.043499514442629e-06</v>
+        <v>0.02901487661877656</v>
       </c>
       <c r="N4" t="n">
-        <v>1.433443915362727</v>
+        <v>1.5381583450687</v>
       </c>
       <c r="O4" t="n">
-        <v>40.3908054873659</v>
+        <v>50.43901896173255</v>
       </c>
       <c r="P4" t="n">
-        <v>12.67818864982808</v>
+        <v>9.833507673504075</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>1.819056555371263</v>
+        <v>2.002017893021911</v>
       </c>
       <c r="S4" t="n">
-        <v>1.683159195121064</v>
+        <v>1.766447488426909</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>2.102977331221916</v>
+        <v>2.33086330656609</v>
       </c>
       <c r="V4" t="n">
-        <v>1.665788737537258</v>
+        <v>1.789742967448009</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>0.9061115534191042</v>
+        <v>0.8701399313793277</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7994480529342389</v>
+        <v>0.7778890112256696</v>
       </c>
     </row>
     <row r="5">
@@ -2499,64 +2499,64 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.140584965189059e-05</v>
+        <v>0.1961373847428318</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0001020515526407746</v>
+        <v>-0.9085858302836218</v>
       </c>
       <c r="D5" t="n">
-        <v>1.100038253870744e-05</v>
+        <v>0.01361794355840536</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-1.195336051564215e-06</v>
+        <v>-0.009523704582232654</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.301912684913207e-06</v>
+        <v>-0.009841641096825287</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>6.198971239514321e-06</v>
+        <v>0.05509227994813838</v>
       </c>
       <c r="J5" t="n">
-        <v>7.127177445949862e-06</v>
+        <v>0.06504959620314882</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>1.68037302312441e-05</v>
+        <v>0.1204873388468129</v>
       </c>
       <c r="M5" t="n">
-        <v>1.672240525918763e-05</v>
+        <v>0.1197916720156098</v>
       </c>
       <c r="N5" t="n">
-        <v>3.799034441861971</v>
+        <v>1.967529521552868</v>
       </c>
       <c r="O5" t="n">
-        <v>-25.14814409892532</v>
+        <v>-29.13555829800933</v>
       </c>
       <c r="P5" t="n">
-        <v>3.143861337206008</v>
+        <v>0.581813795474704</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>-0.2744086268940713</v>
+        <v>-0.2793380527464595</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3002515216403432</v>
+        <v>-0.2894960489461364</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>1.576924944013978</v>
+        <v>1.849929892411405</v>
       </c>
       <c r="V5" t="n">
-        <v>1.815147645069219</v>
+        <v>2.195015252372081</v>
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>3.559098606889074</v>
+        <v>3.503003486690791</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.54954308986924</v>
+        <v>3.483658273858917</v>
       </c>
     </row>
     <row r="6">
@@ -2566,64 +2566,64 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.112625302187589e-05</v>
+        <v>-0.1409348336665263</v>
       </c>
       <c r="C6" t="n">
-        <v>2.419599983967842e-05</v>
+        <v>-0.5955187439362092</v>
       </c>
       <c r="D6" t="n">
-        <v>-6.500865402119576e-06</v>
+        <v>-0.1135764532988314</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1.447933326588542e-05</v>
+        <v>0.0509153025690162</v>
       </c>
       <c r="G6" t="n">
-        <v>1.373812904615641e-05</v>
+        <v>0.04707812421432538</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>5.21294582405736e-06</v>
+        <v>-0.005978252878643051</v>
       </c>
       <c r="J6" t="n">
-        <v>5.022990738018498e-06</v>
+        <v>0.001213637860150611</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>2.66753559184221e-06</v>
+        <v>-0.01219493557429461</v>
       </c>
       <c r="M6" t="n">
-        <v>2.635923572347445e-06</v>
+        <v>-0.01137786529727638</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9365690569190873</v>
+        <v>-1.275822927928711</v>
       </c>
       <c r="O6" t="n">
-        <v>5.933581511027107</v>
+        <v>-20.71308697865224</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.772622750238662</v>
+        <v>-4.440796559789996</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>3.155280707318977</v>
+        <v>1.504557461277936</v>
       </c>
       <c r="S6" t="n">
-        <v>3.012504655799193</v>
+        <v>1.378766267401101</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>1.116404100880009</v>
+        <v>-0.1703672610587856</v>
       </c>
       <c r="V6" t="n">
-        <v>1.076819978115036</v>
+        <v>0.03472596755566827</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>0.4641393805181817</v>
+        <v>-0.2896695083952651</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4589148644791897</v>
+        <v>-0.270809123792713</v>
       </c>
     </row>
     <row r="7">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.569657127830222e-05</v>
+        <v>-0.4167328572216338</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0002009674366390214</v>
+        <v>-1.66396530691701</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.219227072914277e-05</v>
+        <v>-0.1544730763138548</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>-5.40328159421327e-07</v>
+        <v>0.0603438820078307</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.962901862857497e-07</v>
+        <v>0.06420629830587363</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>5.658928954738996e-07</v>
+        <v>0.039194769406443</v>
       </c>
       <c r="J7" t="n">
-        <v>2.701828858122839e-06</v>
+        <v>0.05904984182202236</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>3.508906355767011e-06</v>
+        <v>0.005322857997317179</v>
       </c>
       <c r="M7" t="n">
-        <v>3.490413524586489e-06</v>
+        <v>0.007148329944746426</v>
       </c>
       <c r="N7" t="n">
-        <v>5.572239598597655</v>
+        <v>-4.164554658423637</v>
       </c>
       <c r="O7" t="n">
-        <v>-28.55638642679535</v>
+        <v>-59.31527661778765</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.458948522761869</v>
+        <v>-7.333212585374128</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>-0.1329443675197965</v>
+        <v>1.940948390947645</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1226497051067733</v>
+        <v>2.080935968831499</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>0.1306130331718559</v>
+        <v>1.171519246588346</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6141468961203821</v>
+        <v>1.755496539265965</v>
       </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
-        <v>0.6532926625729952</v>
+        <v>0.1423002803671526</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6492171052311715</v>
+        <v>0.1894911896763585</v>
       </c>
     </row>
     <row r="8">
@@ -2700,64 +2700,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008359892991037045</v>
+        <v>6.4593326430564</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009355492858335252</v>
+        <v>7.093568203128197</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001421437547048364</v>
+        <v>1.091127096670497</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>6.747467142277999e-05</v>
+        <v>0.5923557314864106</v>
       </c>
       <c r="G8" t="n">
-        <v>5.867880011802716e-05</v>
+        <v>0.4998839505098563</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>3.851859403688655e-05</v>
+        <v>0.3363456152920225</v>
       </c>
       <c r="J8" t="n">
-        <v>2.999350984305317e-05</v>
+        <v>0.2538523505675736</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>2.230583209872466e-05</v>
+        <v>0.1879924756699048</v>
       </c>
       <c r="M8" t="n">
-        <v>2.02948521523588e-05</v>
+        <v>0.1692302986139154</v>
       </c>
       <c r="N8" t="n">
-        <v>20.84911294246307</v>
+        <v>20.28137503401554</v>
       </c>
       <c r="O8" t="n">
-        <v>64.47209060572479</v>
+        <v>89.81982608933775</v>
       </c>
       <c r="P8" t="n">
-        <v>19.39009080722289</v>
+        <v>20.80438348808454</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>12.8817547808597</v>
+        <v>14.26599363193059</v>
       </c>
       <c r="S8" t="n">
-        <v>10.7718397910868</v>
+        <v>11.49519726413383</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>7.976634120591425</v>
+        <v>8.861154982356478</v>
       </c>
       <c r="V8" t="n">
-        <v>5.790395647504745</v>
+        <v>6.091979636166847</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
-        <v>5.361411198132108</v>
+        <v>6.093442254449804</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.915772257934359</v>
+        <v>5.60359022753974</v>
       </c>
     </row>
     <row r="9">
@@ -2767,64 +2767,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001917903945760841</v>
+        <v>1.172833359582346</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0003194442311928219</v>
+        <v>2.256066842070086</v>
       </c>
       <c r="D9" t="n">
-        <v>8.76510810904692e-05</v>
+        <v>0.7139328869355401</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>7.053724061927273e-06</v>
+        <v>0.01831966807379258</v>
       </c>
       <c r="G9" t="n">
-        <v>6.651674464681883e-06</v>
+        <v>0.02071489471199291</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>5.023034439273051e-06</v>
+        <v>0.00395008435127268</v>
       </c>
       <c r="J9" t="n">
-        <v>1.803588531412268e-06</v>
+        <v>-0.02588312092779792</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>5.245019559102821e-06</v>
+        <v>0.0335477926817246</v>
       </c>
       <c r="M9" t="n">
-        <v>3.957242862231111e-06</v>
+        <v>0.02216254179327566</v>
       </c>
       <c r="N9" t="n">
-        <v>6.275799282656236</v>
+        <v>4.042440613877582</v>
       </c>
       <c r="O9" t="n">
-        <v>70.72735833436299</v>
+        <v>77.12493271515002</v>
       </c>
       <c r="P9" t="n">
-        <v>16.55631509054641</v>
+        <v>17.81029073365986</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>1.671052000202936</v>
+        <v>0.534283660457036</v>
       </c>
       <c r="S9" t="n">
-        <v>1.613152747242875</v>
+        <v>0.6172550158394056</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>1.20823369769486</v>
+        <v>0.1109443358434403</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4269454207191555</v>
+        <v>-0.7080769509392462</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
-        <v>1.04283437383222</v>
+        <v>0.8166165319181277</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.7836540690768287</v>
+        <v>0.534345011339213</v>
       </c>
     </row>
     <row r="10">
@@ -2834,64 +2834,64 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.000115677184973893</v>
+        <v>0.9199976957179482</v>
       </c>
       <c r="C10" t="n">
-        <v>-5.277578596479194e-05</v>
+        <v>-1.108123142138224</v>
       </c>
       <c r="D10" t="n">
-        <v>4.844381823072828e-05</v>
+        <v>0.3336298868906256</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>2.747356654993558e-06</v>
+        <v>0.01571674163093032</v>
       </c>
       <c r="G10" t="n">
-        <v>1.256055859045377e-06</v>
+        <v>0.0009233948876507846</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>-4.10694115660556e-07</v>
+        <v>-0.0043302925872343</v>
       </c>
       <c r="J10" t="n">
-        <v>1.252691624733042e-08</v>
+        <v>0.006755010923004303</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>-7.416068485459795e-06</v>
+        <v>-0.04660110607691143</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.20530797041095e-06</v>
+        <v>-0.05228012072109908</v>
       </c>
       <c r="N10" t="n">
-        <v>4.387680998820232</v>
+        <v>3.614993415642869</v>
       </c>
       <c r="O10" t="n">
-        <v>-9.345276611768739</v>
+        <v>-27.33606912313407</v>
       </c>
       <c r="P10" t="n">
-        <v>12.16822007336064</v>
+        <v>11.11412981973048</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>0.6788637959004002</v>
+        <v>0.4544018465576496</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3044232398636098</v>
+        <v>0.02503296932212944</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>-0.1007823866002927</v>
+        <v>-0.1231809810180258</v>
       </c>
       <c r="V10" t="n">
-        <v>0.00309373011898723</v>
+        <v>0.1920944987859464</v>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
-        <v>-1.714871441032527</v>
+        <v>-1.239852719173994</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.925776926237241</v>
+        <v>-1.404234151438207</v>
       </c>
     </row>
     <row r="11">
@@ -2901,64 +2901,64 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0001404632498093557</v>
+        <v>1.345985934181509</v>
       </c>
       <c r="C11" t="n">
-        <v>2.651718851049619e-05</v>
+        <v>0.7718025386970675</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.041687747650345e-05</v>
+        <v>-0.09765311396814901</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>7.582381349473545e-06</v>
+        <v>0.04314193176168573</v>
       </c>
       <c r="G11" t="n">
-        <v>6.3700880090233e-06</v>
+        <v>0.03434737346477267</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>4.860463561702875e-06</v>
+        <v>0.03136087666988287</v>
       </c>
       <c r="J11" t="n">
-        <v>4.326485312418334e-06</v>
+        <v>0.01944916175814254</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>2.740896498869078e-07</v>
+        <v>0.005504803612265678</v>
       </c>
       <c r="M11" t="n">
-        <v>3.588610227085513e-07</v>
+        <v>0.006578319052106055</v>
       </c>
       <c r="N11" t="n">
-        <v>5.203302752954905</v>
+        <v>4.994646023311154</v>
       </c>
       <c r="O11" t="n">
-        <v>2.848681086172617</v>
+        <v>16.59623770278021</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.8467193158763</v>
+        <v>-3.51519867479219</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>1.873513475213181</v>
+        <v>1.263465094832414</v>
       </c>
       <c r="S11" t="n">
-        <v>1.585720669615414</v>
+        <v>0.9983215304453138</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>0.9500354656414752</v>
+        <v>0.7403566178855023</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8394239329765855</v>
+        <v>0.4586575369383667</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
-        <v>0.05432966925643938</v>
+        <v>0.1461870334032927</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.07193563094966123</v>
+        <v>0.1764675823474486</v>
       </c>
     </row>
     <row r="12">
@@ -2968,64 +2968,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.70661377188178e-05</v>
+        <v>0.7102315739367174</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001517289643334736</v>
+        <v>1.212560048557472</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.414868285208083e-05</v>
+        <v>-0.09937853712697375</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>7.865287692950517e-06</v>
+        <v>0.03053035248814187</v>
       </c>
       <c r="G12" t="n">
-        <v>7.591058593415654e-06</v>
+        <v>0.03118976624724737</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>2.879282822860568e-06</v>
+        <v>0.004788355857811841</v>
       </c>
       <c r="J12" t="n">
-        <v>1.096775795946317e-06</v>
+        <v>-0.01036632175927085</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>-2.244258841180658e-06</v>
+        <v>0.01701255226238199</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.800585185202907e-06</v>
+        <v>0.01897261115678139</v>
       </c>
       <c r="N12" t="n">
-        <v>2.352899998011222</v>
+        <v>2.982304461546088</v>
       </c>
       <c r="O12" t="n">
-        <v>13.36782549515171</v>
+        <v>29.6232922724275</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.211891626503262</v>
+        <v>-3.398928870177738</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>1.690373594945467</v>
+        <v>0.9148121375870991</v>
       </c>
       <c r="S12" t="n">
-        <v>1.657261175846177</v>
+        <v>0.9827267922471439</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>0.5713563700179243</v>
+        <v>0.1284340089825261</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2125634389484395</v>
+        <v>-0.2738478232264036</v>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>-0.4586910713336508</v>
+        <v>0.4838881205123198</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.3706239597341359</v>
+        <v>0.5433680319168656</v>
       </c>
     </row>
     <row r="13">
@@ -3035,64 +3035,64 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0006691831486558285</v>
+        <v>5.48931546809868</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0004254816844167081</v>
+        <v>3.623129141629798</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.485918185840511e-05</v>
+        <v>0.01550212673616182</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>8.836177371980439e-05</v>
+        <v>0.7517189426736253</v>
       </c>
       <c r="G13" t="n">
-        <v>8.204274534360099e-05</v>
+        <v>0.6762725980369769</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>5.619713794193561e-05</v>
+        <v>0.4853640127473586</v>
       </c>
       <c r="J13" t="n">
-        <v>5.241689579278096e-05</v>
+        <v>0.4409853501116928</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>3.638302200783527e-05</v>
+        <v>0.3295126114691959</v>
       </c>
       <c r="M13" t="n">
-        <v>3.636468607318969e-05</v>
+        <v>0.3288161636164494</v>
       </c>
       <c r="N13" t="n">
-        <v>19.50994772681029</v>
+        <v>18.03398321717534</v>
       </c>
       <c r="O13" t="n">
-        <v>46.7230179848232</v>
+        <v>72.6938773356882</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.965332513005633</v>
+        <v>0.4081477655633273</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>15.35031292272888</v>
+        <v>17.53889311777075</v>
       </c>
       <c r="S13" t="n">
-        <v>14.55720412599482</v>
+        <v>15.08201355541728</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>10.40842786074871</v>
+        <v>12.69669320535511</v>
       </c>
       <c r="V13" t="n">
-        <v>9.441697169957861</v>
+        <v>10.98358631697343</v>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>5.395904944048958</v>
+        <v>6.594800737238969</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.414339475222988</v>
+        <v>6.59700109126647</v>
       </c>
     </row>
     <row r="14">
@@ -3102,64 +3102,64 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.000145755666991713</v>
+        <v>0.9095373688661699</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0003588557446492305</v>
+        <v>2.623832535369325</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0001199110276091121</v>
+        <v>1.045734079831351</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>2.072523894157748e-05</v>
+        <v>0.1153224881123723</v>
       </c>
       <c r="G14" t="n">
-        <v>2.075981266394139e-05</v>
+        <v>0.1220427581147271</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>1.460470701548324e-05</v>
+        <v>0.09322457742609024</v>
       </c>
       <c r="J14" t="n">
-        <v>1.112846784336596e-05</v>
+        <v>0.06094124269292932</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>1.500025050280246e-05</v>
+        <v>0.1073099574459467</v>
       </c>
       <c r="M14" t="n">
-        <v>1.329658729181729e-05</v>
+        <v>0.0894644736120251</v>
       </c>
       <c r="N14" t="n">
-        <v>4.732609234730718</v>
+        <v>3.08317779117836</v>
       </c>
       <c r="O14" t="n">
-        <v>59.68262297828219</v>
+        <v>74.65239169895823</v>
       </c>
       <c r="P14" t="n">
-        <v>17.30506316111613</v>
+        <v>17.7446680354553</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>4.74292465150039</v>
+        <v>3.051711098357814</v>
       </c>
       <c r="S14" t="n">
-        <v>4.756883162239993</v>
+        <v>3.239799626919084</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>3.494265888053783</v>
+        <v>2.572061725879558</v>
       </c>
       <c r="V14" t="n">
-        <v>2.613342983813151</v>
+        <v>1.629151216561615</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
-        <v>3.01064901133516</v>
+        <v>2.804943682986293</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.649017471596361</v>
+        <v>2.298671738981655</v>
       </c>
     </row>
     <row r="15">
@@ -3169,64 +3169,64 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.746730752542794e-05</v>
+        <v>0.4341192942905268</v>
       </c>
       <c r="C15" t="n">
-        <v>-9.732769453935679e-06</v>
+        <v>0.1608151041169829</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.4243886195187e-05</v>
+        <v>-0.1892275145886218</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>1.274570951993922e-05</v>
+        <v>0.07010979179262575</v>
       </c>
       <c r="G15" t="n">
-        <v>1.177408693708166e-05</v>
+        <v>0.0653076541501158</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>4.144061245896089e-06</v>
+        <v>0.003371567869698108</v>
       </c>
       <c r="J15" t="n">
-        <v>4.253870226236974e-06</v>
+        <v>0.003792401754849059</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>2.446260183942081e-06</v>
+        <v>0.004992691067320585</v>
       </c>
       <c r="M15" t="n">
-        <v>2.554855273551638e-06</v>
+        <v>0.005447210078631805</v>
       </c>
       <c r="N15" t="n">
-        <v>2.543038863584663</v>
+        <v>1.63560836158144</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.544028432050743</v>
+        <v>3.446282630119725</v>
       </c>
       <c r="P15" t="n">
-        <v>-7.271471811961203</v>
+        <v>-5.30143170528488</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>2.736879750367283</v>
+        <v>1.693713584439869</v>
       </c>
       <c r="S15" t="n">
-        <v>2.507434412479371</v>
+        <v>1.509574968327915</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>1.056696473818691</v>
+        <v>0.09049544978322439</v>
       </c>
       <c r="V15" t="n">
-        <v>1.088727629943968</v>
+        <v>0.1013036698793178</v>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
-        <v>0.4867680133216368</v>
+        <v>0.1118819144289213</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5106535927217243</v>
+        <v>0.1227080055085196</v>
       </c>
     </row>
     <row r="16">
@@ -3236,64 +3236,64 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0001759909693113827</v>
+        <v>1.994924941266379</v>
       </c>
       <c r="C16" t="n">
-        <v>4.950256267990801e-05</v>
+        <v>0.6822665707952922</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.275310152591886e-05</v>
+        <v>-0.206493446427215</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>5.069699455477479e-06</v>
+        <v>0.02816669499881796</v>
       </c>
       <c r="G16" t="n">
-        <v>3.852218798270547e-06</v>
+        <v>0.01451089695888733</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>1.018869050012568e-05</v>
+        <v>0.09549450980866353</v>
       </c>
       <c r="J16" t="n">
-        <v>9.750024670144687e-06</v>
+        <v>0.08870101249532385</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>5.282326270135203e-06</v>
+        <v>0.0884840281584019</v>
       </c>
       <c r="M16" t="n">
-        <v>5.400381463560167e-06</v>
+        <v>0.08791773171810419</v>
       </c>
       <c r="N16" t="n">
-        <v>6.118354085425642</v>
+        <v>6.660804534298677</v>
       </c>
       <c r="O16" t="n">
-        <v>8.003215174631162</v>
+        <v>16.97004487881244</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.226598558645811</v>
+        <v>-5.886076306125568</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>1.167957585410831</v>
+        <v>0.7814501382372075</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9315680748413335</v>
+        <v>0.4178823482818861</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="n">
-        <v>2.333168160898051</v>
+        <v>2.56545273344127</v>
       </c>
       <c r="V16" t="n">
-        <v>2.259423905126468</v>
+        <v>2.396408245067363</v>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
-        <v>1.143942056673186</v>
+        <v>2.101256366816565</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.170238859504334</v>
+        <v>2.094737478180063</v>
       </c>
     </row>
     <row r="17">
@@ -3303,64 +3303,64 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-4.825775380170735e-06</v>
+        <v>0.7419966974677077</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0001065868361391291</v>
+        <v>-1.113772587826845</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.803471337223509e-05</v>
+        <v>-0.323238430329003</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>4.932188758827476e-06</v>
+        <v>-0.01859961813229552</v>
       </c>
       <c r="G17" t="n">
-        <v>6.071366941144443e-06</v>
+        <v>-0.008927151768805427</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>7.62918515049955e-06</v>
+        <v>0.0237770483422995</v>
       </c>
       <c r="J17" t="n">
-        <v>8.594402137211261e-06</v>
+        <v>0.0365333339780454</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>1.526529150062626e-05</v>
+        <v>0.1024013844517118</v>
       </c>
       <c r="M17" t="n">
-        <v>1.552996028482266e-05</v>
+        <v>0.1066234899731429</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.332606749730247</v>
+        <v>2.820715586486686</v>
       </c>
       <c r="O17" t="n">
-        <v>-20.1907752678693</v>
+        <v>-30.44509829598536</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.862578562735592</v>
+        <v>-8.732507285069101</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>0.9927512359800911</v>
+        <v>-0.4521881108134211</v>
       </c>
       <c r="S17" t="n">
-        <v>1.230654517964598</v>
+        <v>-0.2241226595094761</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="n">
-        <v>1.774837672322672</v>
+        <v>0.6997431232333882</v>
       </c>
       <c r="V17" t="n">
-        <v>2.004390630900835</v>
+        <v>1.069322900205285</v>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
-        <v>3.133321815197327</v>
+        <v>2.615559097110877</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.221276060176372</v>
+        <v>2.760111744929272</v>
       </c>
     </row>
     <row r="18">
@@ -3370,64 +3370,64 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.001578910892695422</v>
+        <v>-8.449257688861289</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.002024675914710954</v>
+        <v>-13.67554549216136</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0003162214611782935</v>
+        <v>-2.128512531077474</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>-0.0001738008827394096</v>
+        <v>-1.421804722105845</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0001581446009611461</v>
+        <v>-1.274466850287166</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>-9.033603057472122e-05</v>
+        <v>-0.7639567583697302</v>
       </c>
       <c r="J18" t="n">
-        <v>-7.227151801155059e-05</v>
+        <v>-0.5995764402578251</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>-4.015957448556026e-05</v>
+        <v>-0.2816357383681948</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.597852259375746e-05</v>
+        <v>-0.2490652179567824</v>
       </c>
       <c r="N18" t="n">
-        <v>-17.45534131743831</v>
+        <v>-10.67658285782493</v>
       </c>
       <c r="O18" t="n">
-        <v>-69.18936874426142</v>
+        <v>-150.3836646469411</v>
       </c>
       <c r="P18" t="n">
-        <v>-20.98431890724</v>
+        <v>-21.53424608966647</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>-18.01984049805619</v>
+        <v>-17.16357671541901</v>
       </c>
       <c r="S18" t="n">
-        <v>-16.88578309900176</v>
+        <v>-15.3581082717345</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="n">
-        <v>-12.51675095876727</v>
+        <v>-9.378089087911402</v>
       </c>
       <c r="V18" t="n">
-        <v>-9.666208343019287</v>
+        <v>-7.176423550291379</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
-        <v>-4.834218716536929</v>
+        <v>-3.363985843962073</v>
       </c>
       <c r="Y18" t="n">
-        <v>-4.280698601383275</v>
+        <v>-2.955206476069252</v>
       </c>
     </row>
     <row r="19">
@@ -3437,64 +3437,64 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0002597808520489792</v>
+        <v>-0.3701818194133415</v>
       </c>
       <c r="C19" t="n">
-        <v>-7.900329941368726e-05</v>
+        <v>-0.776627418102997</v>
       </c>
       <c r="D19" t="n">
-        <v>1.291363792014911e-05</v>
+        <v>-0.0005801023627172232</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>-2.779361308342366e-06</v>
+        <v>-0.08913273261159203</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.288847955510993e-06</v>
+        <v>-0.09012073913238132</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>-1.342036086568334e-05</v>
+        <v>-0.1842252276675046</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.273921829624482e-05</v>
+        <v>-0.1762842524086828</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>-1.613901658649413e-05</v>
+        <v>-0.1214781109177775</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.614815824554843e-05</v>
+        <v>-0.1204367712517752</v>
       </c>
       <c r="N19" t="n">
-        <v>-4.549680164352946</v>
+        <v>-0.639369058090293</v>
       </c>
       <c r="O19" t="n">
-        <v>-9.667542421963425</v>
+        <v>-13.78256195674296</v>
       </c>
       <c r="P19" t="n">
-        <v>2.890044609144482</v>
+        <v>-0.01369512476399372</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>-0.3831919054556923</v>
+        <v>-1.245974752988669</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3142052873993507</v>
+        <v>-1.232522889458598</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="n">
-        <v>-1.95445064521715</v>
+        <v>-2.769340660375805</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.86884595608134</v>
+        <v>-2.664177672416607</v>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
-        <v>-2.085725312261478</v>
+        <v>-1.54897638121797</v>
       </c>
       <c r="Y19" t="n">
-        <v>-2.087950960567476</v>
+        <v>-1.541483883679784</v>
       </c>
     </row>
     <row r="20">
@@ -3504,64 +3504,64 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0001363398259032863</v>
+        <v>0.1366853033943242</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0001135739594720976</v>
+        <v>0.1488611656474143</v>
       </c>
       <c r="D20" t="n">
-        <v>2.640309039244716e-05</v>
+        <v>0.07437920987592664</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>-1.424374570947975e-05</v>
+        <v>-0.1768024736865174</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.156624708391572e-05</v>
+        <v>-0.1521757040559817</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>-3.969081036658794e-06</v>
+        <v>-0.0600679703995978</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.039403687416849e-06</v>
+        <v>-0.06066141703429153</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>-4.044679679579207e-06</v>
+        <v>-0.02925304946513852</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.65374308667885e-06</v>
+        <v>-0.03375562509040315</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.624058638480253</v>
+        <v>0.2183514831306137</v>
       </c>
       <c r="O20" t="n">
-        <v>17.09119737753471</v>
+        <v>2.72429992540132</v>
       </c>
       <c r="P20" t="n">
-        <v>3.942896636154051</v>
+        <v>1.284050746964476</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>-1.526412913392514</v>
+        <v>-1.914124685047274</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.235819711778665</v>
+        <v>-1.635078339750162</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
-        <v>-0.4748552597057306</v>
+        <v>-0.8279304331102318</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6040284902473524</v>
+        <v>-0.8375040411323892</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
-        <v>-0.5183043704347944</v>
+        <v>-0.3954570511458915</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0.5976624470009364</v>
+        <v>-0.459743960745537</v>
       </c>
     </row>
     <row r="21">
@@ -3571,64 +3571,64 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.0001929690184347001</v>
+        <v>-0.4710194700459686</v>
       </c>
       <c r="C21" t="n">
-        <v>-3.344123633689594e-05</v>
+        <v>-1.030703386941869</v>
       </c>
       <c r="D21" t="n">
-        <v>1.665141986739926e-05</v>
+        <v>0.02113914468131005</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>-3.293370652570714e-06</v>
+        <v>-0.1442119415022031</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.549316920653396e-06</v>
+        <v>-0.1300245433342627</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>-3.542927979202738e-06</v>
+        <v>-0.1405741618091878</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.308917546335606e-06</v>
+        <v>-0.127594095758677</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>-1.005546022996719e-05</v>
+        <v>-0.1114849155785266</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.010373036370766e-05</v>
+        <v>-0.1106419916043407</v>
       </c>
       <c r="N21" t="n">
-        <v>-3.356102043814724</v>
+        <v>-0.598603194892227</v>
       </c>
       <c r="O21" t="n">
-        <v>-6.258874462528978</v>
+        <v>-26.56735188675684</v>
       </c>
       <c r="P21" t="n">
-        <v>3.407522565292599</v>
+        <v>0.4129788195054852</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>-0.4294342251848159</v>
+        <v>-1.929695703786552</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2072212612235517</v>
+        <v>-1.872044559897663</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
-        <v>-0.5979870605498587</v>
+        <v>-2.200252020945678</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5634006553673998</v>
+        <v>-2.005952221583124</v>
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
-        <v>-1.455197161787216</v>
+        <v>-1.545327794442593</v>
       </c>
       <c r="Y21" t="n">
-        <v>-1.474012524666929</v>
+        <v>-1.555260147422441</v>
       </c>
     </row>
     <row r="22">
@@ -3638,64 +3638,64 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.0004953405625619866</v>
+        <v>-15.44106455406181</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0001561276324352896</v>
+        <v>-0.589966098341238</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0001261238228273136</v>
+        <v>-1.745447066167197</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>-5.24931123743114e-06</v>
+        <v>0.8658707298290909</v>
       </c>
       <c r="G22" t="n">
-        <v>-9.767955642958941e-07</v>
+        <v>0.949220043753576</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>-4.478113560953846e-06</v>
+        <v>0.5386314296485594</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.279118224411257e-06</v>
+        <v>0.552522808769905</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>2.105996352222962e-06</v>
+        <v>-0.02412497275760618</v>
       </c>
       <c r="M22" t="n">
-        <v>3.863714907112156e-06</v>
+        <v>0.01104181828145629</v>
       </c>
       <c r="N22" t="n">
-        <v>-17.42382642321448</v>
+        <v>-7.6906182502173</v>
       </c>
       <c r="O22" t="n">
-        <v>-14.20932840501837</v>
+        <v>-3.080834653869997</v>
       </c>
       <c r="P22" t="n">
-        <v>-14.14211683472485</v>
+        <v>-9.413508383525288</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>-0.7144153053943455</v>
+        <v>3.073522325527689</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1343379982736142</v>
+        <v>3.395259848423307</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
-        <v>-0.5289191150866571</v>
+        <v>1.702087040358202</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2682663948754354</v>
+        <v>1.74508485094133</v>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
-        <v>0.2265890244842727</v>
+        <v>-0.07592771593068094</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.4169434902383135</v>
+        <v>0.03480395545650303</v>
       </c>
     </row>
     <row r="23">
@@ -3705,64 +3705,64 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7.032168875038334e-05</v>
+        <v>1.152012460679903</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0003376210521266457</v>
+        <v>4.104938189165586</v>
       </c>
       <c r="D23" t="n">
-        <v>7.442898987537844e-05</v>
+        <v>1.31943068716108</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>-2.167337602144993e-05</v>
+        <v>-0.7614231730813176</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.361154055779984e-05</v>
+        <v>-0.7925930203156151</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>-6.17767809838099e-06</v>
+        <v>-0.2188036191818307</v>
       </c>
       <c r="J23" t="n">
-        <v>-9.379117150272018e-06</v>
+        <v>-0.2663324691125175</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>-2.962320494208548e-06</v>
+        <v>-0.03819829995629952</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.890950820899403e-06</v>
+        <v>-0.06294137891161963</v>
       </c>
       <c r="N23" t="n">
-        <v>3.110359880348842</v>
+        <v>2.651945499124146</v>
       </c>
       <c r="O23" t="n">
-        <v>31.46744087999621</v>
+        <v>25.75297278351935</v>
       </c>
       <c r="P23" t="n">
-        <v>8.798691913045834</v>
+        <v>7.756091800656071</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>-1.970449486200396</v>
+        <v>-2.415587268575727</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.147250426474661</v>
+        <v>-2.502776110942454</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="n">
-        <v>-0.5939223026105082</v>
+        <v>-0.6912892206922033</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9017781859849104</v>
+        <v>-0.8398920073510978</v>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="n">
-        <v>-0.2709380450127472</v>
+        <v>-0.1344573167962492</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.3544376543826752</v>
+        <v>-0.2214318064504389</v>
       </c>
     </row>
     <row r="24">
@@ -3772,64 +3772,64 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-7.76172724423756e-05</v>
+        <v>0.9421201056394997</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0003229732422606927</v>
+        <v>0.3962879549630747</v>
       </c>
       <c r="D24" t="n">
-        <v>2.991617692089008e-05</v>
+        <v>0.7029558661328893</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>8.647814716027073e-06</v>
+        <v>0.04366488320926835</v>
       </c>
       <c r="G24" t="n">
-        <v>9.275366951630022e-06</v>
+        <v>0.0311336941001238</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>-3.232662843915773e-06</v>
+        <v>-0.2869247966266277</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.065653440377554e-07</v>
+        <v>-0.293994782037784</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>1.061069966504074e-05</v>
+        <v>0.1453429897071176</v>
       </c>
       <c r="M24" t="n">
-        <v>1.036481589522713e-05</v>
+        <v>0.1397010929314609</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.456504524143962</v>
+        <v>3.464104554824529</v>
       </c>
       <c r="O24" t="n">
-        <v>-21.38862062999051</v>
+        <v>3.343527453095121</v>
       </c>
       <c r="P24" t="n">
-        <v>2.427571621643955</v>
+        <v>4.711945140663193</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>0.5440591479223141</v>
+        <v>0.1836316204904167</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5822077150543276</v>
+        <v>0.1303678493234143</v>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="n">
-        <v>-0.2695727571039015</v>
+        <v>-1.612889111981237</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.02541718243563863</v>
+        <v>-1.649710813469321</v>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="n">
-        <v>0.7162431169371765</v>
+        <v>0.7139186865154148</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.7009650487522729</v>
+        <v>0.6882256670002975</v>
       </c>
     </row>
     <row r="25">
@@ -3839,64 +3839,64 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0001415807612989465</v>
+        <v>-0.2016850436572354</v>
       </c>
       <c r="C25" t="n">
-        <v>0.000307797273731746</v>
+        <v>-0.6732193525581192</v>
       </c>
       <c r="D25" t="n">
-        <v>1.606859704842163e-05</v>
+        <v>-0.1230496255288294</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>1.330984005553035e-05</v>
+        <v>0.2512369271182896</v>
       </c>
       <c r="G25" t="n">
-        <v>1.118615298023026e-05</v>
+        <v>0.2463310826388924</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>7.203996448268895e-06</v>
+        <v>0.3194440221511084</v>
       </c>
       <c r="J25" t="n">
-        <v>4.363013888123823e-06</v>
+        <v>0.3267350097720716</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>-1.537907586743576e-05</v>
+        <v>-0.05909887015953565</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.561152671586943e-05</v>
+        <v>-0.05882386445176339</v>
       </c>
       <c r="N25" t="n">
-        <v>5.115287706760221</v>
+        <v>-0.958141001962462</v>
       </c>
       <c r="O25" t="n">
-        <v>15.89381594868014</v>
+        <v>-6.885035660923336</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9741006265623413</v>
+        <v>-0.9125819602133471</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
-        <v>0.579116736190435</v>
+        <v>1.040968456022145</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4830268323417007</v>
+        <v>1.017657493293843</v>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
-        <v>0.3792857302851655</v>
+        <v>1.536409753590365</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2283095396668485</v>
+        <v>1.573976944160774</v>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
-        <v>-0.7087677134459265</v>
+        <v>-0.2565281869601391</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.7197749310821031</v>
+        <v>-0.2561192518791633</v>
       </c>
     </row>
     <row r="26">
@@ -3906,64 +3906,64 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0002211133318368815</v>
+        <v>1.749211675360383</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0001372042436986591</v>
+        <v>-0.1305794602291019</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.976988113851068e-05</v>
+        <v>-0.2738647387159465</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>-7.892750820495327e-06</v>
+        <v>-0.1198635047338939</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.881904810330985e-06</v>
+        <v>-0.1242311586154935</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>-4.687269491297268e-06</v>
+        <v>-0.1284760494761637</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.424797292770787e-06</v>
+        <v>-0.1266234197786494</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>-1.142989916723124e-05</v>
+        <v>-0.1315162221342635</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.084748586603804e-05</v>
+        <v>-0.1276306224913628</v>
       </c>
       <c r="N26" t="n">
-        <v>8.242441159428569</v>
+        <v>11.25007161017662</v>
       </c>
       <c r="O26" t="n">
-        <v>-12.20409399626433</v>
+        <v>-2.531235960662171</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.903523084578903</v>
+        <v>-4.361314777472183</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>-0.5015890940572639</v>
+        <v>-1.075484804873654</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5032075558620477</v>
+        <v>-1.112689378029211</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="n">
-        <v>-0.2934634675574129</v>
+        <v>-1.145366258638031</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.2144412359816527</v>
+        <v>-1.129965340443931</v>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="n">
-        <v>-0.7309317567202834</v>
+        <v>-1.130900088339531</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.694573873003868</v>
+        <v>-1.099940586334712</v>
       </c>
     </row>
     <row r="27">
@@ -3973,64 +3973,64 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0001886669711094853</v>
+        <v>1.191275262578106</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0004345543722312389</v>
+        <v>2.731908345527017</v>
       </c>
       <c r="D27" t="n">
-        <v>2.784669302316572e-05</v>
+        <v>0.190506751824817</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>1.408165945222956e-05</v>
+        <v>0.09071643665639702</v>
       </c>
       <c r="G27" t="n">
-        <v>1.203905058585705e-05</v>
+        <v>0.07217390429054267</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>1.635512689066401e-05</v>
+        <v>0.1008790418776185</v>
       </c>
       <c r="J27" t="n">
-        <v>1.202668043655244e-05</v>
+        <v>0.0657907166903009</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>9.568414980995682e-06</v>
+        <v>0.06019527991586281</v>
       </c>
       <c r="M27" t="n">
-        <v>8.845683852105022e-06</v>
+        <v>0.05548297543344742</v>
       </c>
       <c r="N27" t="n">
-        <v>18.70623748245881</v>
+        <v>19.25635160992527</v>
       </c>
       <c r="O27" t="n">
-        <v>76.40559005083908</v>
+        <v>92.28011700297293</v>
       </c>
       <c r="P27" t="n">
-        <v>6.349627214444228</v>
+        <v>8.153193746238475</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>4.711057304359272</v>
+        <v>5.500419009910554</v>
       </c>
       <c r="S27" t="n">
-        <v>4.030078436132655</v>
+        <v>4.356934491298641</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="n">
-        <v>5.915056679709036</v>
+        <v>6.232439139632845</v>
       </c>
       <c r="V27" t="n">
-        <v>4.08918637458551</v>
+        <v>3.86100687456974</v>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
-        <v>3.130582921389069</v>
+        <v>3.290573517912443</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.919203972436939</v>
+        <v>3.067714138738448</v>
       </c>
     </row>
     <row r="28">
@@ -4040,64 +4040,64 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.204989353846388e-05</v>
+        <v>0.2472557789797969</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0003536871510594784</v>
+        <v>2.111131596258713</v>
       </c>
       <c r="D28" t="n">
-        <v>0.000128652611988663</v>
+        <v>0.797982008345038</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>7.628956283894066e-06</v>
+        <v>0.0452071224446823</v>
       </c>
       <c r="G28" t="n">
-        <v>7.537040173669994e-06</v>
+        <v>0.04476850771020973</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>4.906834035956205e-06</v>
+        <v>0.0294530925451683</v>
       </c>
       <c r="J28" t="n">
-        <v>1.363585240666002e-06</v>
+        <v>0.002488481827393577</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>6.58034513503438e-06</v>
+        <v>0.03226265864450929</v>
       </c>
       <c r="M28" t="n">
-        <v>4.653062328954376e-06</v>
+        <v>0.01853691224634565</v>
       </c>
       <c r="N28" t="n">
-        <v>4.638764319285638</v>
+        <v>4.317010972323795</v>
       </c>
       <c r="O28" t="n">
-        <v>96.69375972956232</v>
+        <v>106.5206997488666</v>
       </c>
       <c r="P28" t="n">
-        <v>23.92396301843731</v>
+        <v>24.53734617526218</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
-        <v>4.485623716146296</v>
+        <v>4.21550580771786</v>
       </c>
       <c r="S28" t="n">
-        <v>4.495906610336247</v>
+        <v>4.146948612885297</v>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="n">
-        <v>2.490815174287219</v>
+        <v>2.252199379651156</v>
       </c>
       <c r="V28" t="n">
-        <v>0.6372352635659558</v>
+        <v>0.1809142670195221</v>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
-        <v>2.746342974811235</v>
+        <v>2.122690913496689</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.958615756280389</v>
+        <v>1.203436003835237</v>
       </c>
     </row>
     <row r="29">
@@ -4107,64 +4107,64 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.780790013029579e-05</v>
+        <v>0.1981415534760093</v>
       </c>
       <c r="C29" t="n">
-        <v>3.621608584624119e-05</v>
+        <v>0.1971190089936688</v>
       </c>
       <c r="D29" t="n">
-        <v>6.337313026166454e-05</v>
+        <v>0.3992242394393367</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>4.86362692291607e-06</v>
+        <v>0.02444262454751231</v>
       </c>
       <c r="G29" t="n">
-        <v>4.172213124529885e-06</v>
+        <v>0.01953284228406145</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>5.623368135063114e-06</v>
+        <v>0.02554307454829163</v>
       </c>
       <c r="J29" t="n">
-        <v>5.264287856314816e-06</v>
+        <v>0.02263706190887567</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>3.223123934401237e-06</v>
+        <v>0.01138175973838081</v>
       </c>
       <c r="M29" t="n">
-        <v>2.226712942156386e-06</v>
+        <v>0.00459829992365138</v>
       </c>
       <c r="N29" t="n">
-        <v>5.736769672479904</v>
+        <v>4.181213714219921</v>
       </c>
       <c r="O29" t="n">
-        <v>13.68381790607941</v>
+        <v>13.60855124753203</v>
       </c>
       <c r="P29" t="n">
-        <v>20.241855050984</v>
+        <v>21.69803425750031</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>2.646532770331917</v>
+        <v>2.180641250055246</v>
       </c>
       <c r="S29" t="n">
-        <v>2.256077329933425</v>
+        <v>1.724659562570986</v>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="n">
-        <v>2.626921920526109</v>
+        <v>1.880565460059004</v>
       </c>
       <c r="V29" t="n">
-        <v>2.46298466782204</v>
+        <v>1.663171942181364</v>
       </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
-        <v>1.382027890135716</v>
+        <v>0.8366051186858284</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.946757192610974</v>
+        <v>0.335904443226048</v>
       </c>
     </row>
     <row r="30">
@@ -4174,64 +4174,64 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-2.776876040908658e-05</v>
+        <v>-0.1984596744490122</v>
       </c>
       <c r="C30" t="n">
-        <v>-4.611459029450579e-05</v>
+        <v>-0.4370480626120442</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.633197357885488e-05</v>
+        <v>-0.1149519725186328</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
-        <v>4.79976130098376e-06</v>
+        <v>0.02883908188986144</v>
       </c>
       <c r="G30" t="n">
-        <v>5.004385352352496e-06</v>
+        <v>0.03144178635953124</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>6.687876988387872e-06</v>
+        <v>0.03524777252306772</v>
       </c>
       <c r="J30" t="n">
-        <v>7.097200877201353e-06</v>
+        <v>0.04062273922626401</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>5.684312079057627e-06</v>
+        <v>0.03397337903143162</v>
       </c>
       <c r="M30" t="n">
-        <v>5.751220561314945e-06</v>
+        <v>0.03545126873773022</v>
       </c>
       <c r="N30" t="n">
-        <v>-3.710321671660028</v>
+        <v>-3.667798858904919</v>
       </c>
       <c r="O30" t="n">
-        <v>-14.66707295782198</v>
+        <v>-21.07035626840899</v>
       </c>
       <c r="P30" t="n">
-        <v>-6.055110753053979</v>
+        <v>-7.772737135123187</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>2.093716598750748</v>
+        <v>2.073333531807517</v>
       </c>
       <c r="S30" t="n">
-        <v>2.189928289002285</v>
+        <v>2.283830823144479</v>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="n">
-        <v>3.195790677495205</v>
+        <v>2.644973077793109</v>
       </c>
       <c r="V30" t="n">
-        <v>3.355757368999807</v>
+        <v>3.017763002876344</v>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
-        <v>2.28252657140254</v>
+        <v>2.147004905153096</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.298496207594156</v>
+        <v>2.246619284900107</v>
       </c>
     </row>
     <row r="31">
@@ -4241,64 +4241,64 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-6.463194606908119e-05</v>
+        <v>-0.4168469304611218</v>
       </c>
       <c r="C31" t="n">
-        <v>-6.584664805177794e-05</v>
+        <v>-0.5943068797269305</v>
       </c>
       <c r="D31" t="n">
-        <v>-3.478449906242104e-06</v>
+        <v>-0.08506881184822164</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>4.517027952562295e-07</v>
+        <v>-0.008835695339369584</v>
       </c>
       <c r="G31" t="n">
-        <v>8.239776815964027e-07</v>
+        <v>-0.005525765522700964</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>3.23761530232431e-07</v>
+        <v>-0.0109073952754144</v>
       </c>
       <c r="J31" t="n">
-        <v>8.681177361205536e-07</v>
+        <v>-0.00281217737997925</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>2.985597458101365e-06</v>
+        <v>0.005491624923167075</v>
       </c>
       <c r="M31" t="n">
-        <v>2.94350479363437e-06</v>
+        <v>0.006922130315170987</v>
       </c>
       <c r="N31" t="n">
-        <v>-10.79748082466959</v>
+        <v>-9.415779554861446</v>
       </c>
       <c r="O31" t="n">
-        <v>-17.90501332625025</v>
+        <v>-22.16278121177304</v>
       </c>
       <c r="P31" t="n">
-        <v>-1.583686733985812</v>
+        <v>-6.362728006304247</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>0.2074026029932642</v>
+        <v>-0.7142630099822667</v>
       </c>
       <c r="S31" t="n">
-        <v>0.3803738445670273</v>
+        <v>-0.4522882928180845</v>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="n">
-        <v>0.1378080731325069</v>
+        <v>-0.772011157585881</v>
       </c>
       <c r="V31" t="n">
-        <v>0.370837083677323</v>
+        <v>-0.1992257577830614</v>
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
-        <v>1.304957827510133</v>
+        <v>0.3833383500259214</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.293239846260271</v>
+        <v>0.4846591499139547</v>
       </c>
     </row>
     <row r="32">
@@ -4308,13 +4308,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13.19154503717972</v>
+        <v>15.92891343072914</v>
       </c>
       <c r="C32" t="n">
-        <v>36.52299635818959</v>
+        <v>45.89757168280669</v>
       </c>
       <c r="D32" t="n">
-        <v>3.09356992962293</v>
+        <v>3.762422357624928</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>

--- a/outputs/05_benchmark_signals/tables_v_viii/us/table_viii_image_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/us/table_viii_image_logit.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="display" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="display_stars" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="raw" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2178,6 +2179,1770 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>(6)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>(7)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>(9)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>(10)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>(11)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>(12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2.24***</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.99***</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2.61***</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1.15***</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1.06***</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.70***</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>open_lag1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-2.03***</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-0.85***</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.05**</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-0.14***</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-0.12***</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>open_lag2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.68***</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.29***</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.08**</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.07*</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.09**</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.07*</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>open_lag3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.20**</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-0.91***</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.06*</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.07**</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.12***</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.12***</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>open_lag4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-0.60***</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-0.11***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>open_lag5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-0.42***</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-1.66***</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-0.15***</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.06*</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.06**</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.06*</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>high_lag1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6.46***</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7.09***</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.09***</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.59***</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.50***</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.34***</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.25***</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.19***</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.17***</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>high_lag2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.17***</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2.26***</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.71***</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>high_lag3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.92***</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-1.11***</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.33***</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>high_lag4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.35***</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.77***</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-0.10***</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>high_lag5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.71***</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.21***</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-0.10***</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>low_lag1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5.49***</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.62***</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.75***</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.68***</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.49***</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.44***</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.33***</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.33***</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>low_lag2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.91***</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2.62***</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.05***</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.12***</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.12***</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.09**</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.11***</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.09**</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>low_lag3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.16***</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-0.19***</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.07*</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>low_lag4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.99***</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.68***</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.21***</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.10**</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.09**</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0.09**</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0.09**</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>low_lag5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.74***</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-1.11***</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.32***</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.10***</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0.11***</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>close_lag1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-8.45***</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-13.68***</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-2.13***</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-1.42***</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-1.27***</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.76***</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.60***</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.28***</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.25***</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>close_lag2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-0.78***</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.18***</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-0.18***</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>close_lag3</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.15***</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-0.18*</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>close_lag4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-1.03***</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-0.14*</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-0.13*</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.14**</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-0.13**</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ma_lag1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>-15.44***</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-0.59***</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-1.75***</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0.87***</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.95***</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.54*</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.55*</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ma_lag2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1.15***</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4.10***</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1.32***</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-0.76**</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-0.79**</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ma_lag3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.94***</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.40***</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.70***</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-0.29*</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ma_lag4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-0.67***</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ma_lag5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1.75***</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>-0.13**</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-0.27***</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>vol_lag1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1.19***</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2.73***</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.19***</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0.09***</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.07***</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.10***</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.07***</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0.06***</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>0.06***</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>vol_lag2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0.25***</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2.11***</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.80***</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0.05***</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.04***</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.03**</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0.03**</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>vol_lag3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0.20***</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.20***</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.40***</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0.02**</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.02*</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.03*</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.02*</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>vol_lag4</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>-0.20***</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>-0.44***</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>-0.11***</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0.03**</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.03**</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.04***</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.04***</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0.03**</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>0.04**</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>vol_lag5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>-0.42***</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-0.59***</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>-0.09***</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>McFadden R²</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>15.93</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>45.90</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OOS McFadden R²</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Y33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/outputs/05_benchmark_signals/tables_v_viii/us/table_viii_image_logit.xlsx
+++ b/outputs/05_benchmark_signals/tables_v_viii/us/table_viii_image_logit.xlsx
@@ -2158,15 +2158,51 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3922,15 +3958,51 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6112,15 +6184,33 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>0.2563246479063808</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5896517471116969</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.03803661055042928</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.09125143120014556</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.2811008651014135</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-0.2119101950456947</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.5567760526045351</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.262240142080028</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-0.9218440855818022</v>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
